--- a/crates/xlstream-eval/tests/fixtures/operators/comparison.xlsx
+++ b/crates/xlstream-eval/tests/fixtures/operators/comparison.xlsx
@@ -9,6 +9,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet name="TextCompare" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -20,12 +21,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
-  <si>
-    <t xml:space="preserve">id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">val</t>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="23">
+  <si>
+    <t xml:space="preserve">a</t>
+  </si>
+  <si>
+    <t xml:space="preserve">b</t>
   </si>
   <si>
     <t xml:space="preserve">eq</t>
@@ -44,6 +45,51 @@
   </si>
   <si>
     <t xml:space="preserve">gte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eq_zero</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eq_neg</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text_eq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">text_neq</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t1</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">abc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ABC</t>
+  </si>
+  <si>
+    <t xml:space="preserve">def</t>
+  </si>
+  <si>
+    <t xml:space="preserve">z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hello</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TEST</t>
   </si>
 </sst>
 </file>
@@ -320,7 +366,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H11"/>
+  <dimension ref="A1:L11"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -348,21 +394,33 @@
       <c r="H1" s="0" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="0" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="0" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="0" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="0" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="0" t="n">
         <v>10</v>
       </c>
       <c r="B2" s="0" t="n">
-        <v>3.5</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1" t="b">
         <f aca="false">(A2=B2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D2" s="1" t="b">
         <f aca="false">(A2&lt;&gt;B2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E2" s="1" t="b">
         <f aca="false">(A2&lt;B2)</f>
@@ -370,23 +428,31 @@
       </c>
       <c r="F2" s="1" t="b">
         <f aca="false">(A2&gt;B2)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G2" s="1" t="b">
         <f aca="false">(A2&lt;=B2)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1" t="b">
         <f aca="false">(A2&gt;=B2)</f>
         <v>1</v>
       </c>
+      <c r="I2" s="1" t="b">
+        <f aca="false">(A2=0)</f>
+        <v>0</v>
+      </c>
+      <c r="J2" s="1" t="b">
+        <f aca="false">(A2=-5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="0" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="B3" s="0" t="n">
-        <v>7.2</v>
+        <v>20</v>
       </c>
       <c r="C3" s="1" t="b">
         <f aca="false">(A3=B3)</f>
@@ -398,35 +464,43 @@
       </c>
       <c r="E3" s="1" t="b">
         <f aca="false">(A3&lt;B3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3" s="1" t="b">
         <f aca="false">(A3&gt;B3)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G3" s="1" t="b">
         <f aca="false">(A3&lt;=B3)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H3" s="1" t="b">
         <f aca="false">(A3&gt;=B3)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I3" s="1" t="b">
+        <f aca="false">(A3=0)</f>
+        <v>0</v>
+      </c>
+      <c r="J3" s="1" t="b">
+        <f aca="false">(A3=-5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="0" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="B4" s="0" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="C4" s="1" t="b">
         <f aca="false">(A4=B4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D4" s="1" t="b">
         <f aca="false">(A4&lt;&gt;B4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E4" s="1" t="b">
         <f aca="false">(A4&lt;B4)</f>
@@ -434,31 +508,39 @@
       </c>
       <c r="F4" s="1" t="b">
         <f aca="false">(A4&gt;B4)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1" t="b">
         <f aca="false">(A4&lt;=B4)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H4" s="1" t="b">
         <f aca="false">(A4&gt;=B4)</f>
         <v>1</v>
       </c>
+      <c r="I4" s="1" t="b">
+        <f aca="false">(A4=0)</f>
+        <v>0</v>
+      </c>
+      <c r="J4" s="1" t="b">
+        <f aca="false">(A4=-5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="0" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="B5" s="0" t="n">
-        <v>15.8</v>
+        <v>0</v>
       </c>
       <c r="C5" s="1" t="b">
         <f aca="false">(A5=B5)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D5" s="1" t="b">
         <f aca="false">(A5&lt;&gt;B5)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5" s="1" t="b">
         <f aca="false">(A5&lt;B5)</f>
@@ -466,15 +548,23 @@
       </c>
       <c r="F5" s="1" t="b">
         <f aca="false">(A5&gt;B5)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1" t="b">
         <f aca="false">(A5&lt;=B5)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1" t="b">
         <f aca="false">(A5&gt;=B5)</f>
         <v>1</v>
+      </c>
+      <c r="I5" s="1" t="b">
+        <f aca="false">(A5=0)</f>
+        <v>1</v>
+      </c>
+      <c r="J5" s="1" t="b">
+        <f aca="false">(A5=-5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -482,7 +572,7 @@
         <v>-5</v>
       </c>
       <c r="B6" s="0" t="n">
-        <v>-2.3</v>
+        <v>5</v>
       </c>
       <c r="C6" s="1" t="b">
         <f aca="false">(A6=B6)</f>
@@ -508,21 +598,29 @@
         <f aca="false">(A6&gt;=B6)</f>
         <v>0</v>
       </c>
+      <c r="I6" s="1" t="b">
+        <f aca="false">(A6=0)</f>
+        <v>0</v>
+      </c>
+      <c r="J6" s="1" t="b">
+        <f aca="false">(A6=-5)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="0" t="n">
-        <v>50</v>
+        <v>-5</v>
       </c>
       <c r="B7" s="0" t="n">
-        <v>8.1</v>
+        <v>-5</v>
       </c>
       <c r="C7" s="1" t="b">
         <f aca="false">(A7=B7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="b">
         <f aca="false">(A7&lt;&gt;B7)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7" s="1" t="b">
         <f aca="false">(A7&lt;B7)</f>
@@ -530,31 +628,39 @@
       </c>
       <c r="F7" s="1" t="b">
         <f aca="false">(A7&gt;B7)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="1" t="b">
         <f aca="false">(A7&lt;=B7)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="1" t="b">
         <f aca="false">(A7&gt;=B7)</f>
         <v>1</v>
       </c>
+      <c r="I7" s="1" t="b">
+        <f aca="false">(A7=0)</f>
+        <v>0</v>
+      </c>
+      <c r="J7" s="1" t="b">
+        <f aca="false">(A7=-5)</f>
+        <v>1</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="0" t="n">
-        <v>75</v>
+        <v>3.14</v>
       </c>
       <c r="B8" s="0" t="n">
-        <v>4.6</v>
+        <v>3.14</v>
       </c>
       <c r="C8" s="1" t="b">
         <f aca="false">(A8=B8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D8" s="1" t="b">
         <f aca="false">(A8&lt;&gt;B8)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8" s="1" t="b">
         <f aca="false">(A8&lt;B8)</f>
@@ -562,23 +668,31 @@
       </c>
       <c r="F8" s="1" t="b">
         <f aca="false">(A8&gt;B8)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G8" s="1" t="b">
         <f aca="false">(A8&lt;=B8)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="1" t="b">
         <f aca="false">(A8&gt;=B8)</f>
         <v>1</v>
       </c>
+      <c r="I8" s="1" t="b">
+        <f aca="false">(A8=0)</f>
+        <v>0</v>
+      </c>
+      <c r="J8" s="1" t="b">
+        <f aca="false">(A8=-5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="0" t="n">
-        <v>1</v>
+        <v>3.14</v>
       </c>
       <c r="B9" s="0" t="n">
-        <v>0.5</v>
+        <v>3.15</v>
       </c>
       <c r="C9" s="1" t="b">
         <f aca="false">(A9=B9)</f>
@@ -590,27 +704,35 @@
       </c>
       <c r="E9" s="1" t="b">
         <f aca="false">(A9&lt;B9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" s="1" t="b">
         <f aca="false">(A9&gt;B9)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="1" t="b">
         <f aca="false">(A9&lt;=B9)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H9" s="1" t="b">
         <f aca="false">(A9&gt;=B9)</f>
-        <v>1</v>
+        <v>0</v>
+      </c>
+      <c r="I9" s="1" t="b">
+        <f aca="false">(A9=0)</f>
+        <v>0</v>
+      </c>
+      <c r="J9" s="1" t="b">
+        <f aca="false">(A9=-5)</f>
+        <v>0</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="0" t="n">
-        <v>999</v>
+        <v>100</v>
       </c>
       <c r="B10" s="0" t="n">
-        <v>12.4</v>
+        <v>0</v>
       </c>
       <c r="C10" s="1" t="b">
         <f aca="false">(A10=B10)</f>
@@ -636,13 +758,21 @@
         <f aca="false">(A10&gt;=B10)</f>
         <v>1</v>
       </c>
+      <c r="I10" s="1" t="b">
+        <f aca="false">(A10=0)</f>
+        <v>0</v>
+      </c>
+      <c r="J10" s="1" t="b">
+        <f aca="false">(A10=-5)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="0" t="n">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="B11" s="0" t="n">
-        <v>6.7</v>
+        <v>-1</v>
       </c>
       <c r="C11" s="1" t="b">
         <f aca="false">(A11=B11)</f>
@@ -667,6 +797,287 @@
       <c r="H11" s="1" t="b">
         <f aca="false">(A11&gt;=B11)</f>
         <v>1</v>
+      </c>
+      <c r="I11" s="1" t="b">
+        <f aca="false">(A11=0)</f>
+        <v>1</v>
+      </c>
+      <c r="J11" s="1" t="b">
+        <f aca="false">(A11=-5)</f>
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" s="0" t="s">
+        <v>13</v>
+      </c>
+      <c r="C1" s="0" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="0" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="0" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="1" t="b">
+        <f aca="false">(A2=B2)</f>
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="b">
+        <f aca="false">(A2&lt;&gt;B2)</f>
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="b">
+        <f aca="false">(A2&lt;B2)</f>
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="b">
+        <f aca="false">(A2&gt;B2)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B3" s="0" t="s">
+        <v>15</v>
+      </c>
+      <c r="C3" s="1" t="b">
+        <f aca="false">(A3=B3)</f>
+        <v>1</v>
+      </c>
+      <c r="D3" s="1" t="b">
+        <f aca="false">(A3&lt;&gt;B3)</f>
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="b">
+        <f aca="false">(A3&lt;B3)</f>
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="b">
+        <f aca="false">(A3&gt;B3)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="1" t="b">
+        <f aca="false">(A4=B4)</f>
+        <v>0</v>
+      </c>
+      <c r="D4" s="1" t="b">
+        <f aca="false">(A4&lt;&gt;B4)</f>
+        <v>1</v>
+      </c>
+      <c r="E4" s="1" t="b">
+        <f aca="false">(A4&lt;B4)</f>
+        <v>1</v>
+      </c>
+      <c r="F4" s="1" t="b">
+        <f aca="false">(A4&gt;B4)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="C5" s="1" t="b">
+        <f aca="false">(A5=B5)</f>
+        <v>1</v>
+      </c>
+      <c r="D5" s="1" t="b">
+        <f aca="false">(A5&lt;&gt;B5)</f>
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="b">
+        <f aca="false">(A5&lt;B5)</f>
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="b">
+        <f aca="false">(A5&gt;B5)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="0" t="s">
+        <v>1</v>
+      </c>
+      <c r="C6" s="1" t="b">
+        <f aca="false">(A6=B6)</f>
+        <v>0</v>
+      </c>
+      <c r="D6" s="1" t="b">
+        <f aca="false">(A6&lt;&gt;B6)</f>
+        <v>1</v>
+      </c>
+      <c r="E6" s="1" t="b">
+        <f aca="false">(A6&lt;B6)</f>
+        <v>1</v>
+      </c>
+      <c r="F6" s="1" t="b">
+        <f aca="false">(A6&gt;B6)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="0" t="s">
+        <v>17</v>
+      </c>
+      <c r="B7" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="C7" s="1" t="b">
+        <f aca="false">(A7=B7)</f>
+        <v>0</v>
+      </c>
+      <c r="D7" s="1" t="b">
+        <f aca="false">(A7&lt;&gt;B7)</f>
+        <v>1</v>
+      </c>
+      <c r="E7" s="1" t="b">
+        <f aca="false">(A7&lt;B7)</f>
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="b">
+        <f aca="false">(A7&gt;B7)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="C8" s="1" t="b">
+        <f aca="false">(A8=B8)</f>
+        <v>1</v>
+      </c>
+      <c r="D8" s="1" t="b">
+        <f aca="false">(A8&lt;&gt;B8)</f>
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="b">
+        <f aca="false">(A8&lt;B8)</f>
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="b">
+        <f aca="false">(A8&gt;B8)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="0" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="0" t="s">
+        <v>0</v>
+      </c>
+      <c r="C9" s="1" t="b">
+        <f aca="false">(A9=B9)</f>
+        <v>1</v>
+      </c>
+      <c r="D9" s="1" t="b">
+        <f aca="false">(A9&lt;&gt;B9)</f>
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="b">
+        <f aca="false">(A9&lt;B9)</f>
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="b">
+        <f aca="false">(A9&gt;B9)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="C10" s="1" t="b">
+        <f aca="false">(A10=B10)</f>
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="b">
+        <f aca="false">(A10&lt;&gt;B10)</f>
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="b">
+        <f aca="false">(A10&lt;B10)</f>
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="b">
+        <f aca="false">(A10&gt;B10)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="0" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" s="0" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="1" t="b">
+        <f aca="false">(A11=B11)</f>
+        <v>1</v>
+      </c>
+      <c r="D11" s="1" t="b">
+        <f aca="false">(A11&lt;&gt;B11)</f>
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="b">
+        <f aca="false">(A11&lt;B11)</f>
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="b">
+        <f aca="false">(A11&gt;B11)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
